--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_49.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3591113.67161436</v>
+        <v>3584246.678665702</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034355</v>
+        <v>10041900.99034356</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034355</v>
+        <v>10041900.99034356</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162898915</v>
+        <v>286.41071628997</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162898915</v>
+        <v>286.41071628997</v>
       </c>
     </row>
     <row r="11">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>189.3139912864829</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>147.1964482685823</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>215.3817731139785</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>186.6627672578626</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>385</v>
+        <v>366.2103592575547</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1033,13 +1033,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172589</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>277.9274879340253</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,22 +1213,22 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>140.7678969571885</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>167.1158402638075</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>385</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172477</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
-        <v>50.21035976018675</v>
+        <v>114.9504353879267</v>
       </c>
       <c r="V12" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>49.39139276613435</v>
@@ -1650,13 +1650,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U14" t="n">
         <v>299.2212965486107</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.55655664632661</v>
+        <v>230.1079332804206</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
         <v>53.75737228701621</v>
@@ -1896,7 +1896,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V17" t="n">
         <v>279.8510241668239</v>
@@ -1921,13 +1921,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="E18" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2091,7 +2091,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
         <v>58.00965870352741</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2158,7 +2158,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09991244551929</v>
+        <v>206.6512890796133</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>22.47211154361427</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>197.2737972923793</v>
@@ -2316,7 +2316,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D23" t="n">
         <v>60.33915573984979</v>
@@ -2376,7 +2376,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X23" t="n">
         <v>242.2818334606677</v>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>104.5622219498565</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>239.5984974349628</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2692,7 +2692,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X27" t="n">
         <v>69.86273944538755</v>
@@ -2790,7 +2790,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D29" t="n">
         <v>60.33915573984979</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>277.7834726314007</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U30" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856292</v>
       </c>
       <c r="V30" t="n">
         <v>64.51066719152016</v>
@@ -3078,7 +3078,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T32" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U32" t="n">
         <v>299.2212965486107</v>
@@ -3087,7 +3087,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X32" t="n">
         <v>242.2818334606677</v>
@@ -3109,10 +3109,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>64.74007562773993</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>70.00566530352994</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
-        <v>118.0355277429563</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>131.9993129555745</v>
+        <v>135.964704340989</v>
       </c>
       <c r="C38" t="n">
         <v>99.47457824299391</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3580,7 +3580,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>73.77767497096173</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
@@ -3643,7 +3643,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>69.86273944538755</v>
+        <v>265.4141160794816</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3829,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3871,7 +3871,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U42" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V42" t="n">
         <v>64.51066719152016</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4029,7 +4029,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>279.8510241668239</v>
@@ -4066,10 +4066,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>156.8009660958027</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>129.9010681051558</v>
       </c>
     </row>
     <row r="46">
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="D3" t="n">
-        <v>705.9632657544848</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="E3" t="n">
         <v>359.8298342171994</v>
@@ -4433,19 +4433,19 @@
         <v>964.8227613033797</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>575.9338724144908</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>561.2766328270967</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>528.5764884737346</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>508.5131152965754</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685.313758878083</v>
+        <v>947.896520609007</v>
       </c>
       <c r="C4" t="n">
-        <v>811.3157646965188</v>
+        <v>1073.898526427443</v>
       </c>
       <c r="D4" t="n">
-        <v>811.3157646965188</v>
+        <v>1073.898526427443</v>
       </c>
       <c r="E4" t="n">
-        <v>929.1446689079319</v>
+        <v>1073.898526427443</v>
       </c>
       <c r="F4" t="n">
-        <v>929.1446689079319</v>
+        <v>1198.259499019378</v>
       </c>
       <c r="G4" t="n">
-        <v>1082.551234794817</v>
+        <v>1351.666064906264</v>
       </c>
       <c r="H4" t="n">
-        <v>1082.551234794817</v>
+        <v>1521.182650065661</v>
       </c>
       <c r="I4" t="n">
-        <v>1082.551234794817</v>
+        <v>1540</v>
       </c>
       <c r="J4" t="n">
-        <v>1443.634975447269</v>
+        <v>1540</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>314.6014477324597</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>513.4228406184056</v>
+        <v>664.2482646830374</v>
       </c>
       <c r="W4" t="n">
-        <v>685.313758878083</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="X4" t="n">
-        <v>685.313758878083</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="Y4" t="n">
-        <v>685.313758878083</v>
+        <v>836.1391829427148</v>
       </c>
     </row>
     <row r="5">
@@ -4570,13 +4570,13 @@
         <v>793.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="P5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4585,7 +4585,7 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
         <v>1226.636423316867</v>
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
       <c r="C6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
       <c r="D6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
       <c r="E6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>648.582120073203</v>
+        <v>492.7340146711483</v>
       </c>
       <c r="T6" t="n">
-        <v>643.1702360151082</v>
+        <v>487.3221306130535</v>
       </c>
       <c r="U6" t="n">
-        <v>642.9577514088589</v>
+        <v>487.1096460068043</v>
       </c>
       <c r="V6" t="n">
-        <v>628.3005118214649</v>
+        <v>472.4524064194102</v>
       </c>
       <c r="W6" t="n">
-        <v>239.4116229325759</v>
+        <v>439.752262066048</v>
       </c>
       <c r="X6" t="n">
-        <v>219.3482497554168</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="Y6" t="n">
-        <v>219.3482497554168</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>740.6187813286217</v>
+        <v>392.6703525618345</v>
       </c>
       <c r="C7" t="n">
-        <v>866.6207871470575</v>
+        <v>392.6703525618345</v>
       </c>
       <c r="D7" t="n">
-        <v>866.6207871470575</v>
+        <v>392.6703525618345</v>
       </c>
       <c r="E7" t="n">
-        <v>984.4496913584705</v>
+        <v>510.4992567732476</v>
       </c>
       <c r="F7" t="n">
-        <v>984.4496913584705</v>
+        <v>634.860229365183</v>
       </c>
       <c r="G7" t="n">
-        <v>984.4496913584705</v>
+        <v>788.2667952520683</v>
       </c>
       <c r="H7" t="n">
-        <v>984.4496913584705</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="I7" t="n">
-        <v>1205.582570294554</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063134</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
-        <v>1540.000000000003</v>
+        <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
@@ -4746,22 +4746,22 @@
         <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>218.8756791588049</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>218.8756791588049</v>
+        <v>109.3701336231249</v>
       </c>
       <c r="V7" t="n">
-        <v>417.6970720447508</v>
+        <v>109.3701336231249</v>
       </c>
       <c r="W7" t="n">
-        <v>589.5879903044282</v>
+        <v>281.2610518828023</v>
       </c>
       <c r="X7" t="n">
-        <v>740.6187813286217</v>
+        <v>281.2610518828023</v>
       </c>
       <c r="Y7" t="n">
-        <v>740.6187813286217</v>
+        <v>392.6703525618345</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.9500000000016</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>411.9500000000016</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
-        <v>411.9500000000016</v>
+        <v>411.95</v>
       </c>
       <c r="M8" t="n">
-        <v>777.6999999999954</v>
+        <v>793.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1158.849999999999</v>
+        <v>1174.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.849999999999</v>
+        <v>1174.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.849999999999</v>
+        <v>1174.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4828,19 +4828,19 @@
         <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>508.5131152965754</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>508.5131152965754</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>508.5131152965754</v>
+        <v>545.7373105916365</v>
       </c>
       <c r="E9" t="n">
-        <v>508.5131152965754</v>
+        <v>199.603879054351</v>
       </c>
       <c r="F9" t="n">
-        <v>366.3233203903244</v>
+        <v>199.603879054351</v>
       </c>
       <c r="G9" t="n">
-        <v>366.3233203903244</v>
+        <v>199.603879054351</v>
       </c>
       <c r="H9" t="n">
-        <v>30.8</v>
+        <v>199.603879054351</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4907,19 +4907,19 @@
         <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>575.9338724144908</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>561.2766328270967</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>528.5764884737346</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>508.5131152965754</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>508.5131152965754</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>539.7741901789475</v>
+        <v>670.4378910406568</v>
       </c>
       <c r="C10" t="n">
-        <v>665.7761959973833</v>
+        <v>670.4378910406568</v>
       </c>
       <c r="D10" t="n">
-        <v>665.7761959973833</v>
+        <v>670.4378910406568</v>
       </c>
       <c r="E10" t="n">
-        <v>783.6051002087963</v>
+        <v>788.2667952520699</v>
       </c>
       <c r="F10" t="n">
-        <v>783.6051002087963</v>
+        <v>788.2667952520699</v>
       </c>
       <c r="G10" t="n">
-        <v>783.6051002087963</v>
+        <v>788.2667952520699</v>
       </c>
       <c r="H10" t="n">
-        <v>953.1216853681939</v>
+        <v>957.7833804114674</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.55182541068</v>
+        <v>1178.91625934755</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063132</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="K10" t="n">
-        <v>1540</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
@@ -4986,19 +4986,19 @@
         <v>256.125934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>256.125934252978</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>256.125934252978</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="W10" t="n">
-        <v>428.0168525126554</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="X10" t="n">
-        <v>428.0168525126554</v>
+        <v>653.7079179154581</v>
       </c>
       <c r="Y10" t="n">
-        <v>428.0168525126554</v>
+        <v>670.4378910406568</v>
       </c>
     </row>
     <row r="11">
@@ -5032,25 +5032,25 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1662.388828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>2215.798828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P11" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1091.779612404716</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C12" t="n">
-        <v>1080.567579631464</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="E12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="F12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="H12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="J12" t="n">
-        <v>1204.524099806763</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K12" t="n">
-        <v>1393.716915901147</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L12" t="n">
-        <v>1665.067377496347</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M12" t="n">
-        <v>1751.147919239206</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N12" t="n">
-        <v>1884.428203846775</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O12" t="n">
-        <v>2123.470655530493</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P12" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2036.733538088506</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>1918.992123982838</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>1863.075189419693</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>1812.357654308393</v>
+        <v>711.1160588913324</v>
       </c>
       <c r="V12" t="n">
-        <v>1683.884492978128</v>
+        <v>645.9537687988877</v>
       </c>
       <c r="W12" t="n">
-        <v>1600.679298119715</v>
+        <v>562.7485739404751</v>
       </c>
       <c r="X12" t="n">
-        <v>1176.575520902152</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y12" t="n">
-        <v>1126.685225178784</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="13">
@@ -5272,31 +5272,31 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L14" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T14" t="n">
         <v>1846.617029377474</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D15" t="n">
-        <v>461.5662247731743</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E15" t="n">
-        <v>461.5662247731743</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F15" t="n">
-        <v>380.2433203903244</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G15" t="n">
-        <v>380.2433203903244</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H15" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I15" t="n">
         <v>44.72</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
         <v>157.615990899539</v>
@@ -5506,19 +5506,19 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L17" t="n">
-        <v>1151.54</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M17" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N17" t="n">
-        <v>1704.95</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O17" t="n">
         <v>1797.400904947332</v>
@@ -5539,19 +5539,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
         <v>108.0308712378207</v>
       </c>
       <c r="D18" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
         <v>44.72</v>
@@ -5630,7 +5630,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
         <v>946.5478354584615</v>
@@ -5700,16 +5700,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
         <v>103.3156148520479</v>
@@ -5743,25 +5743,25 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L20" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M20" t="n">
-        <v>555.568828728935</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N20" t="n">
-        <v>1108.978828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O20" t="n">
-        <v>1662.388828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="P20" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5770,25 +5770,25 @@
         <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>297.950717050992</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D21" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E21" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F21" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G21" t="n">
-        <v>286.7386842777402</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H21" t="n">
         <v>264.0395817084329</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>332.8563298250593</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C22" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D22" t="n">
         <v>1010.366979583462</v>
@@ -5931,22 +5931,22 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X22" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y22" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="23">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
         <v>328.9211162073474</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L23" t="n">
-        <v>989.4391130376558</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M23" t="n">
-        <v>989.4391130376558</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N23" t="n">
-        <v>989.4391130376558</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>1542.849113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6019,13 +6019,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>402.0654643105373</v>
+        <v>297.950717050992</v>
       </c>
       <c r="C24" t="n">
-        <v>390.8534315372855</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="D24" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
         <v>44.72</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>332.8563298250593</v>
       </c>
     </row>
     <row r="25">
@@ -6129,7 +6129,7 @@
         <v>1161.267639059017</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
         <v>1377.480007433093</v>
@@ -6217,22 +6217,22 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L26" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M26" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O26" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>1797.400904947332</v>
@@ -6320,19 +6320,19 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W27" t="n">
         <v>274.6072361907174</v>
@@ -6433,46 +6433,46 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="L29" t="n">
-        <v>989.4391130376558</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M29" t="n">
-        <v>989.4391130376558</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N29" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O29" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P29" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G30" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>919.5630540741914</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>801.8216399685234</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>745.9047054053782</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U30" t="n">
-        <v>695.1871702940784</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V30" t="n">
-        <v>630.0248802016338</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W30" t="n">
-        <v>546.8196853432211</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X30" t="n">
-        <v>476.2512616610114</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y30" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="31">
@@ -6691,25 +6691,25 @@
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>598.13</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M32" t="n">
-        <v>1108.978828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N32" t="n">
-        <v>1108.978828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6721,13 +6721,13 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
         <v>970.4091539265823</v>
@@ -6752,19 +6752,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D33" t="n">
-        <v>110.1140157855959</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>115.4327932358888</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>115.4327932358888</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>115.4327932358888</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>115.4327932358888</v>
       </c>
       <c r="I33" t="n">
         <v>44.72</v>
@@ -6879,7 +6879,7 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U34" t="n">
         <v>372.6360891248843</v>
@@ -6940,13 +6940,13 @@
         <v>1500.287941766591</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -7037,7 +7037,7 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
         <v>713.1992034391076</v>
@@ -7119,16 +7119,16 @@
         <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
         <v>807.7884919737335</v>
@@ -7168,16 +7168,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="L38" t="n">
-        <v>1542.849113037656</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M38" t="n">
-        <v>2053.697941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="N38" t="n">
-        <v>2236</v>
+        <v>1682.59</v>
       </c>
       <c r="O38" t="n">
         <v>2236</v>
@@ -7189,28 +7189,28 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7271,25 +7271,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>204.0388125085078</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851397</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="40">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
         <v>1010.366979583462</v>
@@ -7362,13 +7362,13 @@
         <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7402,25 +7402,25 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="L41" t="n">
-        <v>1286.552076218397</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="M41" t="n">
-        <v>1797.400904947332</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N41" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504074</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V42" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7590,16 +7590,16 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
         <v>745.8791912947012</v>
@@ -7639,37 +7639,37 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L44" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M44" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
         <v>1544.373295489988</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.9618669904511</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C45" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D45" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E45" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F45" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7760,10 +7760,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>469.7577754878864</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>419.8674797645184</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="46">
@@ -7773,19 +7773,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
         <v>1257.463422273695</v>
@@ -7842,7 +7842,7 @@
         <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -8213,16 +8213,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450919</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>913.7065720867555</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698384</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.822684327487</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,10 +8675,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8693,10 +8693,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q11" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
         <v>559</v>
@@ -8927,13 +8927,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>211.4002806471673</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,22 +9149,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K17" t="n">
         <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>163.6326220461452</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>257.410082171668</v>
       </c>
       <c r="Q20" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>257.410082171668</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>777.3630622928068</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>544.2621276423173</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>211.4002806471676</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,13 +10349,13 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>206.6237041381304</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10583,16 +10583,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>661.3924512348951</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,19 +10811,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>536.4141414141418</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1141042229713</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>536.4141414141417</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>629.2478695740924</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646053286</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646054422</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1542690.093990435</v>
+        <v>1542690.093990434</v>
       </c>
       <c r="C2" t="n">
         <v>1542690.093990435</v>
@@ -26278,7 +26278,7 @@
         <v>1542690.093990435</v>
       </c>
       <c r="E2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542736.874407428</v>
       </c>
       <c r="F2" t="n">
         <v>1542736.874407429</v>
@@ -26308,10 +26308,10 @@
         <v>1542736.874407429</v>
       </c>
       <c r="O2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542736.874407428</v>
       </c>
       <c r="P2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542736.874407428</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.3728533789</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>779220.3690909258</v>
+        <v>777704.5134026095</v>
       </c>
       <c r="C6" t="n">
-        <v>916798.3492247401</v>
+        <v>915282.4935364245</v>
       </c>
       <c r="D6" t="n">
-        <v>918859.1211370558</v>
+        <v>917343.2654487399</v>
       </c>
       <c r="E6" t="n">
-        <v>594983.4711808934</v>
+        <v>593241.6213677855</v>
       </c>
       <c r="F6" t="n">
-        <v>938174.366526398</v>
+        <v>936432.5167132898</v>
       </c>
       <c r="G6" t="n">
-        <v>940119.9429945833</v>
+        <v>938378.093181476</v>
       </c>
       <c r="H6" t="n">
-        <v>942068.2198118843</v>
+        <v>940326.3699987774</v>
       </c>
       <c r="I6" t="n">
-        <v>944019.2164552453</v>
+        <v>942277.3666421372</v>
       </c>
       <c r="J6" t="n">
-        <v>530452.9526568697</v>
+        <v>528711.1028437623</v>
       </c>
       <c r="K6" t="n">
-        <v>947929.4484090891</v>
+        <v>946187.5985959815</v>
       </c>
       <c r="L6" t="n">
-        <v>949888.7239693488</v>
+        <v>948146.874156241</v>
       </c>
       <c r="M6" t="n">
-        <v>890602.7998653281</v>
+        <v>888860.9500522201</v>
       </c>
       <c r="N6" t="n">
-        <v>953815.6969001814</v>
+        <v>952073.847087074</v>
       </c>
       <c r="O6" t="n">
-        <v>675783.4361579194</v>
+        <v>674041.5863448115</v>
       </c>
       <c r="P6" t="n">
-        <v>957754.0390089296</v>
+        <v>956012.1891958216</v>
       </c>
     </row>
   </sheetData>
@@ -27027,10 +27027,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27082,7 +27082,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
         <v>174</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27518,10 +27518,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>158.6236956112197</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>195.4756489533303</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27600,25 +27600,25 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
         <v>400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>195.6408797962181</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>385.8591824402657</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
-      </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27721,10 +27721,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
+        <v>400</v>
+      </c>
+      <c r="T5" t="n">
         <v>371.2938086145853</v>
-      </c>
-      <c r="T5" t="n">
-        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>139.0767686171647</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>81.5639999646113</v>
+        <v>100.3536407070566</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>14.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27831,7 +27831,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>285.5362180555555</v>
@@ -27840,22 +27840,22 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>261.5851061779086</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>230.3221626109477</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y7" t="n">
         <v>400</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27964,7 +27964,7 @@
         <v>400</v>
       </c>
       <c r="U8" t="n">
-        <v>371.2938086145854</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27992,22 +27992,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>198.8683453806883</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>50.01054562754106</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28043,7 +28043,7 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>15.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -28086,13 +28086,13 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>293.2295566731349</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X10" t="n">
         <v>400</v>
       </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
-      </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>304.3643156021884</v>
       </c>
     </row>
     <row r="11">
@@ -28229,7 +28229,7 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
@@ -28280,16 +28280,16 @@
         <v>350</v>
       </c>
       <c r="U12" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="V12" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W12" t="n">
         <v>350</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y12" t="n">
         <v>350</v>
@@ -28429,13 +28429,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
       </c>
       <c r="T14" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U14" t="n">
         <v>350</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28472,16 +28472,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>259.1265669988554</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28630,7 +28630,7 @@
         <v>350</v>
       </c>
       <c r="F17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G17" t="n">
         <v>350</v>
@@ -28675,7 +28675,7 @@
         <v>350</v>
       </c>
       <c r="U17" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -28700,13 +28700,13 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E18" t="n">
-        <v>279.9943346964702</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -28779,7 +28779,7 @@
         <v>350</v>
       </c>
       <c r="C19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D19" t="n">
         <v>350</v>
@@ -28836,7 +28836,7 @@
         <v>350</v>
       </c>
       <c r="V19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W19" t="n">
         <v>350</v>
@@ -28870,7 +28870,7 @@
         <v>350</v>
       </c>
       <c r="G20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H20" t="n">
         <v>350</v>
@@ -28906,7 +28906,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28937,7 +28937,7 @@
         <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -28952,7 +28952,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>309.6959756428068</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>350</v>
@@ -29019,55 +29019,55 @@
         <v>350</v>
       </c>
       <c r="D22" t="n">
+        <v>350</v>
+      </c>
+      <c r="E22" t="n">
+        <v>350</v>
+      </c>
+      <c r="F22" t="n">
+        <v>350</v>
+      </c>
+      <c r="G22" t="n">
+        <v>350</v>
+      </c>
+      <c r="H22" t="n">
+        <v>350</v>
+      </c>
+      <c r="I22" t="n">
+        <v>350</v>
+      </c>
+      <c r="J22" t="n">
+        <v>350</v>
+      </c>
+      <c r="K22" t="n">
+        <v>350</v>
+      </c>
+      <c r="L22" t="n">
+        <v>350</v>
+      </c>
+      <c r="M22" t="n">
+        <v>350</v>
+      </c>
+      <c r="N22" t="n">
+        <v>350</v>
+      </c>
+      <c r="O22" t="n">
+        <v>350</v>
+      </c>
+      <c r="P22" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>350</v>
+      </c>
+      <c r="R22" t="n">
+        <v>350</v>
+      </c>
+      <c r="S22" t="n">
+        <v>350</v>
+      </c>
+      <c r="T22" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E22" t="n">
-        <v>350</v>
-      </c>
-      <c r="F22" t="n">
-        <v>350</v>
-      </c>
-      <c r="G22" t="n">
-        <v>350</v>
-      </c>
-      <c r="H22" t="n">
-        <v>350</v>
-      </c>
-      <c r="I22" t="n">
-        <v>350</v>
-      </c>
-      <c r="J22" t="n">
-        <v>350</v>
-      </c>
-      <c r="K22" t="n">
-        <v>350</v>
-      </c>
-      <c r="L22" t="n">
-        <v>350</v>
-      </c>
-      <c r="M22" t="n">
-        <v>350</v>
-      </c>
-      <c r="N22" t="n">
-        <v>350</v>
-      </c>
-      <c r="O22" t="n">
-        <v>350</v>
-      </c>
-      <c r="P22" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>350</v>
-      </c>
-      <c r="R22" t="n">
-        <v>350</v>
-      </c>
-      <c r="S22" t="n">
-        <v>350</v>
-      </c>
-      <c r="T22" t="n">
-        <v>350</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29095,7 +29095,7 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D23" t="n">
         <v>350</v>
@@ -29155,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="W23" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X23" t="n">
         <v>350</v>
@@ -29171,16 +29171,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="C24" t="n">
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>108.3391894627398</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29265,10 +29265,10 @@
         <v>350</v>
       </c>
       <c r="G25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="H25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I25" t="n">
         <v>350</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29471,7 +29471,7 @@
         <v>350</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X27" t="n">
         <v>350</v>
@@ -29569,7 +29569,7 @@
         <v>350</v>
       </c>
       <c r="C29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D29" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29663,7 +29663,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29693,16 +29693,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
       </c>
       <c r="T30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -29857,16 +29857,16 @@
         <v>350</v>
       </c>
       <c r="T32" t="n">
+        <v>350</v>
+      </c>
+      <c r="U32" t="n">
+        <v>350</v>
+      </c>
+      <c r="V32" t="n">
+        <v>350</v>
+      </c>
+      <c r="W32" t="n">
         <v>346.0346086145854</v>
-      </c>
-      <c r="U32" t="n">
-        <v>350</v>
-      </c>
-      <c r="V32" t="n">
-        <v>350</v>
-      </c>
-      <c r="W32" t="n">
-        <v>350</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29888,10 +29888,10 @@
         <v>350</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>277.9320215941727</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29903,7 +29903,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>147.1207205878186</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -30015,10 +30015,10 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
+        <v>350</v>
+      </c>
+      <c r="U34" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U34" t="n">
-        <v>350</v>
       </c>
       <c r="V34" t="n">
         <v>350</v>
@@ -30173,10 +30173,10 @@
         <v>350</v>
       </c>
       <c r="T36" t="n">
+        <v>350</v>
+      </c>
+      <c r="U36" t="n">
         <v>287.3222374745575</v>
-      </c>
-      <c r="U36" t="n">
-        <v>350</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30255,19 +30255,19 @@
         <v>350</v>
       </c>
       <c r="U37" t="n">
+        <v>350</v>
+      </c>
+      <c r="V37" t="n">
+        <v>350</v>
+      </c>
+      <c r="W37" t="n">
+        <v>350</v>
+      </c>
+      <c r="X37" t="n">
+        <v>350</v>
+      </c>
+      <c r="Y37" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="V37" t="n">
-        <v>350</v>
-      </c>
-      <c r="W37" t="n">
-        <v>350</v>
-      </c>
-      <c r="X37" t="n">
-        <v>350</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>350</v>
       </c>
     </row>
     <row r="38">
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="C38" t="n">
         <v>350</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30359,7 +30359,7 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30407,7 +30407,7 @@
         <v>350</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
@@ -30422,7 +30422,7 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30441,7 +30441,7 @@
         <v>350</v>
       </c>
       <c r="D40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E40" t="n">
         <v>350</v>
@@ -30498,7 +30498,7 @@
         <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30608,13 +30608,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>130.1881592409333</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30650,7 +30650,7 @@
         <v>350</v>
       </c>
       <c r="U42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30808,7 +30808,7 @@
         <v>350</v>
       </c>
       <c r="U44" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V44" t="n">
         <v>350</v>
@@ -30845,10 +30845,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30896,10 +30896,10 @@
         <v>350</v>
       </c>
       <c r="X45" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
     </row>
     <row r="46">
@@ -30924,61 +30924,61 @@
         <v>350</v>
       </c>
       <c r="G46" t="n">
+        <v>350</v>
+      </c>
+      <c r="H46" t="n">
+        <v>350</v>
+      </c>
+      <c r="I46" t="n">
+        <v>350</v>
+      </c>
+      <c r="J46" t="n">
+        <v>350</v>
+      </c>
+      <c r="K46" t="n">
+        <v>350</v>
+      </c>
+      <c r="L46" t="n">
+        <v>350</v>
+      </c>
+      <c r="M46" t="n">
+        <v>350</v>
+      </c>
+      <c r="N46" t="n">
+        <v>350</v>
+      </c>
+      <c r="O46" t="n">
+        <v>350</v>
+      </c>
+      <c r="P46" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>350</v>
+      </c>
+      <c r="S46" t="n">
+        <v>350</v>
+      </c>
+      <c r="T46" t="n">
+        <v>350</v>
+      </c>
+      <c r="U46" t="n">
+        <v>350</v>
+      </c>
+      <c r="V46" t="n">
+        <v>350</v>
+      </c>
+      <c r="W46" t="n">
+        <v>350</v>
+      </c>
+      <c r="X46" t="n">
+        <v>350</v>
+      </c>
+      <c r="Y46" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="H46" t="n">
-        <v>350</v>
-      </c>
-      <c r="I46" t="n">
-        <v>350</v>
-      </c>
-      <c r="J46" t="n">
-        <v>350</v>
-      </c>
-      <c r="K46" t="n">
-        <v>350</v>
-      </c>
-      <c r="L46" t="n">
-        <v>350</v>
-      </c>
-      <c r="M46" t="n">
-        <v>350</v>
-      </c>
-      <c r="N46" t="n">
-        <v>350</v>
-      </c>
-      <c r="O46" t="n">
-        <v>350</v>
-      </c>
-      <c r="P46" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>350</v>
-      </c>
-      <c r="R46" t="n">
-        <v>350</v>
-      </c>
-      <c r="S46" t="n">
-        <v>350</v>
-      </c>
-      <c r="T46" t="n">
-        <v>350</v>
-      </c>
-      <c r="U46" t="n">
-        <v>350</v>
-      </c>
-      <c r="V46" t="n">
-        <v>350</v>
-      </c>
-      <c r="W46" t="n">
-        <v>350</v>
-      </c>
-      <c r="X46" t="n">
-        <v>350</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34886,25 +34886,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>19.00742417609984</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>97.33840863912272</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34992,16 +34992,16 @@
         <v>385</v>
       </c>
       <c r="N5" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,7 +35117,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -35126,22 +35126,22 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>226.3161573420008</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,22 +35168,22 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>79.36377133648978</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385.0000000000016</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,10 +35226,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>369.4444444444382</v>
+        <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>385.0000000000032</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385.0000000000016</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -35372,13 +35372,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>116.5961010530166</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>16.898962752726</v>
       </c>
     </row>
     <row r="11">
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -35472,10 +35472,10 @@
         <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
         <v>559</v>
@@ -35706,13 +35706,13 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,22 +35928,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K17" t="n">
         <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>559</v>
-      </c>
-      <c r="O17" t="n">
-        <v>93.38475247205275</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36065,7 +36065,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C19" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D19" t="n">
         <v>64.46378194444452</v>
@@ -36122,7 +36122,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W19" t="n">
         <v>123.6271901612903</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36305,7 +36305,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D22" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E22" t="n">
         <v>69.01909516304346</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N23" t="n">
         <v>559</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>257.1230221309866</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36551,10 +36551,10 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>104.95612715847</v>
+        <v>97.1674577926042</v>
       </c>
       <c r="H25" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I25" t="n">
         <v>173.3665443798817</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>300.1141042229716</v>
+        <v>559</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>141.1524110730751</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
         <v>559</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,13 +37113,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
         <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37128,13 +37128,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37301,10 +37301,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596762</v>
       </c>
       <c r="V34" t="n">
         <v>150.8296897837838</v>
@@ -37362,16 +37362,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37541,7 +37541,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
         <v>150.8296897837838</v>
@@ -37553,7 +37553,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
     <row r="38">
@@ -37590,19 +37590,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37727,7 +37727,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E40" t="n">
         <v>69.01909516304346</v>
@@ -37784,7 +37784,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>115.8385207954244</v>
+        <v>123.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>536.4141414141418</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>559</v>
       </c>
-      <c r="L41" t="n">
-        <v>300.1141042229713</v>
-      </c>
-      <c r="M41" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>536.4141414141417</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>559</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38210,7 +38210,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>97.1674577926042</v>
+        <v>104.95612715847</v>
       </c>
       <c r="H46" t="n">
         <v>121.2288738983814</v>
@@ -38264,7 +38264,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
   </sheetData>
